--- a/data/trans_orig/IP11B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP11B-Provincia-trans_orig.xlsx
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4646</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,14%</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2938</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6840</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>6654</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11434</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>94,22%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2961</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3559</t>
+          <t>2966</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1327</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2432</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,7 +1957,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,69%</t>
+          <t>65,14%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3067</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>25,98%</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3856</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2194</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1789</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>47,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,7 +2737,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,52%</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2366</t>
+          <t>2265</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2724</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3796</t>
+          <t>3394</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4521</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6306</t>
+          <t>6328</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4168</t>
+          <t>4605</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>13621</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3186</t>
+          <t>2545</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3547,7 +3547,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>18,3%</t>
         </is>
       </c>
     </row>
@@ -4144,7 +4144,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>2514</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>61,04%</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1179</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>58,5%</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5621,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>2723</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>49,29%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5656,7 +5656,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4115</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>662</t>
+          <t>661</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>4756</t>
+          <t>5366</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -5729,12 +5729,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2047</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6176</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5744,12 +5744,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>90,14%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7688</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>77,93%</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3420</t>
+          <t>2820</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>49,96%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4834</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5897,7 +5897,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>708</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6236</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>2716</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5995,7 +5995,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3322</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6010,7 +6010,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>4059</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6045,7 +6045,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -6108,7 +6108,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4519</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6123,7 +6123,7 @@
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6373,7 +6373,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>3399</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>21,68%</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6431,7 +6431,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6446,12 +6446,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>515</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4262</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6480</t>
+          <t>6630</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>49,44%</t>
         </is>
       </c>
     </row>
@@ -6524,12 +6524,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>450</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4058</t>
+          <t>3577</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6539,12 +6539,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>73,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6559,12 +6559,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2241</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>3878</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9288</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>69,26%</t>
         </is>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6657,7 +6657,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6677,7 +6677,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3884</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6707,12 +6707,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>747</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,22%</t>
         </is>
       </c>
     </row>
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>5858</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7133,7 +7133,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6809</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7178,12 +7178,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -7206,12 +7206,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>1975</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>8297</t>
+          <t>8180</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7221,12 +7221,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3776</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>11105</t>
+          <t>11637</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7256,12 +7256,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>6131</t>
+          <t>6185</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16463</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7291,12 +7291,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,12%</t>
         </is>
       </c>
     </row>
@@ -7319,12 +7319,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>18283</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>27220</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7334,12 +7334,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7354,12 +7354,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>26480</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>36636</t>
+          <t>36597</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>47364</t>
+          <t>48353</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>61619</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -7432,12 +7432,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>8712</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7467,12 +7467,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>6564</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>16626</t>
+          <t>15879</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -7565,7 +7565,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -7635,7 +7635,7 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3868</t>
+          <t>3648</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,11%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>2649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>516</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>504</t>
+          <t>575</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4511</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>79,73%</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8503,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4257</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8538,7 +8538,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4331</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>75,75%</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2784</t>
+          <t>2749</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3258</t>
+          <t>2994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>52,91%</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8994,7 +8994,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9009,7 +9009,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -9032,12 +9032,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1320</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6340</t>
+          <t>6385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9047,12 +9047,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9072,7 +9072,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9102,12 +9102,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8208</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9117,12 +9117,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2104</t>
+          <t>2049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7506</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8281</t>
+          <t>7959</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14327</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,02%</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>488</t>
+          <t>569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4397</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6752</t>
+          <t>6661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -9411,7 +9411,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3983</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9426,7 +9426,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9446,7 +9446,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4052</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -9754,7 +9754,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3635</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9804,7 +9804,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7944</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9955,7 +9955,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9975,7 +9975,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9594</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>19463</t>
+          <t>19732</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>24394</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3378</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10108,7 +10108,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,5%</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10599,7 +10599,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>43,91%</t>
         </is>
       </c>
     </row>
@@ -10662,7 +10662,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>49,12%</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>3900</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10825,7 +10825,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>53,3%</t>
         </is>
       </c>
     </row>
@@ -10853,7 +10853,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2726</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10883,7 +10883,7 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -10918,12 +10918,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1949</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6680</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10933,12 +10933,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,12%</t>
         </is>
       </c>
     </row>
@@ -11600,7 +11600,7 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>681</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
@@ -11615,7 +11615,7 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -11718,7 +11718,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2693</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>67,3%</t>
         </is>
       </c>
     </row>
@@ -11831,7 +11831,7 @@
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,93%</t>
         </is>
       </c>
     </row>
@@ -12139,7 +12139,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>5463</t>
+          <t>5396</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -12287,7 +12287,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>3489</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>49,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -12360,12 +12360,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7463</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>12441</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -12375,12 +12375,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -12395,12 +12395,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>13073</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>19529</t>
+          <t>19571</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,06%</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12478,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -12493,7 +12493,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -12513,7 +12513,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -12528,7 +12528,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -12739,7 +12739,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>18,87%</t>
         </is>
       </c>
     </row>
@@ -12899,7 +12899,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3408</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -12914,7 +12914,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -12929,12 +12929,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>694</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6478</t>
+          <t>6930</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -12944,12 +12944,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -12964,12 +12964,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7364</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -12979,12 +12979,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,35%</t>
         </is>
       </c>
     </row>
@@ -13042,12 +13042,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>700</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6286</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -13057,12 +13057,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -13077,12 +13077,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>696</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>7428</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -13092,12 +13092,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>22,91%</t>
         </is>
       </c>
     </row>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>7891</t>
+          <t>7387</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13135,7 +13135,7 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
@@ -13155,12 +13155,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9225</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>16578</t>
+          <t>16474</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -13170,12 +13170,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -13190,12 +13190,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19294</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>27715</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -13205,12 +13205,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,5%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -13273,7 +13273,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>2775</t>
+          <t>3170</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -13323,7 +13323,7 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -13386,7 +13386,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -13807,7 +13807,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>2516</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -13822,7 +13822,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>54,15%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>2832</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -13857,7 +13857,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -13877,7 +13877,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>41,26%</t>
         </is>
       </c>
     </row>
@@ -13915,12 +13915,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1827</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,39%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -13950,7 +13950,7 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>704</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -13985,12 +13985,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8430</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -14000,12 +14000,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14033,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2502</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -14048,7 +14048,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>3759</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,61%</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2536</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>3158</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>32,63%</t>
         </is>
       </c>
     </row>
@@ -14489,7 +14489,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>4459</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -14519,12 +14519,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>2381</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>10594</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -14539,7 +14539,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3114</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>12550</t>
+          <t>12409</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -14569,12 +14569,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -14597,12 +14597,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>1988</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>9477</t>
+          <t>9250</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -14612,12 +14612,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -14632,12 +14632,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>2742</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -14647,12 +14647,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -14667,12 +14667,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>16429</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -14682,12 +14682,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,13%</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14710,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>33557</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>43776</t>
+          <t>43479</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -14725,12 +14725,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -14745,12 +14745,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>40474</t>
+          <t>40594</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>54533</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -14760,12 +14760,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -14780,12 +14780,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>77831</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94970</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -14795,12 +14795,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,92%</t>
         </is>
       </c>
     </row>
@@ -14823,12 +14823,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>1863</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>8417</t>
+          <t>8069</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -14838,12 +14838,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -14858,12 +14858,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>7047</t>
+          <t>6866</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>18110</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -14873,12 +14873,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -14893,12 +14893,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>22696</t>
+          <t>23048</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,43%</t>
         </is>
       </c>
     </row>
@@ -14941,7 +14941,7 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5029</t>
+          <t>4923</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -14956,7 +14956,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -14971,12 +14971,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>5829</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -14986,12 +14986,12 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -15006,12 +15006,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>8157</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -15021,12 +15021,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>3519</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -15069,7 +15069,7 @@
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
@@ -15124,7 +15124,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -15139,7 +15139,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -15703,7 +15703,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2950</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>33,75%</t>
         </is>
       </c>
     </row>
@@ -15776,7 +15776,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -15811,12 +15811,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3484</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7951</t>
+          <t>7991</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -15826,12 +15826,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3734</t>
+          <t>4227</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -16022,7 +16022,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -16042,7 +16042,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4713</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -16057,7 +16057,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -16315,7 +16315,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3192</t>
+          <t>2540</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>47,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -16385,7 +16385,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>3413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -16536,12 +16536,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4757</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -16551,12 +16551,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -16571,12 +16571,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1965</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6103</t>
+          <t>6114</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -16586,12 +16586,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -16606,12 +16606,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4653</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10134</t>
+          <t>10113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -16621,12 +16621,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -16654,7 +16654,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2798</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -16669,7 +16669,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -16689,7 +16689,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -16704,7 +16704,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -16719,12 +16719,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -16734,12 +16734,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,39%</t>
         </is>
       </c>
     </row>
@@ -16767,7 +16767,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -16802,7 +16802,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -16817,7 +16817,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -16832,12 +16832,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>631</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>4550</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -16847,12 +16847,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -17905,7 +17905,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2564</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -17920,7 +17920,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -17940,7 +17940,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -17955,7 +17955,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3994</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -17990,7 +17990,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2734</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -18068,7 +18068,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -18088,7 +18088,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2803</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -18103,7 +18103,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -18126,12 +18126,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4299</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -18141,12 +18141,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -18161,12 +18161,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -18176,12 +18176,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -18196,12 +18196,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4709</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10505</t>
+          <t>10530</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -18211,12 +18211,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3517</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,11%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -18279,7 +18279,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2805</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -18294,7 +18294,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -18357,7 +18357,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -18372,7 +18372,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -18427,7 +18427,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -19786,7 +19786,7 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>5890</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
@@ -19801,7 +19801,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>61,87%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3551</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -19919,7 +19919,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>35,94%</t>
         </is>
       </c>
     </row>
@@ -19982,7 +19982,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>2964</t>
+          <t>2984</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -19997,7 +19997,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>49,95%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -20017,7 +20017,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>3497</t>
+          <t>2948</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -20032,7 +20032,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>30,97%</t>
         </is>
       </c>
     </row>
@@ -20546,12 +20546,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3374</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -20561,12 +20561,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -20581,12 +20581,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>5320</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -20596,12 +20596,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,88%</t>
         </is>
       </c>
     </row>
@@ -20694,12 +20694,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>4746</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -20709,12 +20709,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -20777,7 +20777,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2767</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -20792,7 +20792,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>67,49%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -20812,7 +20812,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2814</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -20827,7 +20827,7 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>42,78%</t>
         </is>
       </c>
     </row>
@@ -21198,7 +21198,7 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>2195</t>
+          <t>2192</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>70,3%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -21233,7 +21233,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -21248,7 +21248,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -21263,12 +21263,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>535</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -21278,12 +21278,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>42,26%</t>
         </is>
       </c>
     </row>
@@ -21306,7 +21306,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>559</t>
+          <t>884</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -21321,7 +21321,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
@@ -21341,12 +21341,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2503</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6520</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -21356,12 +21356,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -21376,12 +21376,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>8618</t>
+          <t>8759</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -21391,12 +21391,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>84,53%</t>
         </is>
       </c>
     </row>
@@ -21424,7 +21424,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2064</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -21439,7 +21439,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4067</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -21474,7 +21474,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -21494,7 +21494,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4177</t>
+          <t>3935</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>37,97%</t>
         </is>
       </c>
     </row>
@@ -21685,7 +21685,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2621</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -21700,7 +21700,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -21735,7 +21735,7 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -21880,7 +21880,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>3544</t>
+          <t>3482</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -21895,7 +21895,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -21915,7 +21915,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -21930,7 +21930,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -21945,12 +21945,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>553</t>
+          <t>558</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -21960,12 +21960,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3731</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -22008,7 +22008,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -22023,12 +22023,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1789</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>7960</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -22038,12 +22038,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -22058,12 +22058,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8411</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -22073,12 +22073,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -22101,12 +22101,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>9567</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -22116,12 +22116,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -22136,12 +22136,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>22243</t>
+          <t>22276</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>32129</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -22151,12 +22151,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>54,7%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -22171,12 +22171,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>34325</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,29%</t>
         </is>
       </c>
     </row>
@@ -22214,12 +22214,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9451</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -22229,12 +22229,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -22249,12 +22249,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8261</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -22264,12 +22264,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -22284,12 +22284,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -22299,12 +22299,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -22327,12 +22327,12 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>622</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>5254</t>
+          <t>5129</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -22342,12 +22342,12 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -22362,12 +22362,12 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1404</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>8117</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -22382,7 +22382,7 @@
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -22397,12 +22397,12 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>11355</t>
+          <t>10827</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
@@ -22412,12 +22412,12 @@
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -22480,7 +22480,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3416</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>3191</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -22530,7 +22530,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -22981,7 +22981,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4464</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -22996,7 +22996,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -23202,7 +23202,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2078</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -23217,7 +23217,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -23320,7 +23320,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3612</t>
+          <t>3788</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>54,51%</t>
         </is>
       </c>
     </row>
@@ -23776,7 +23776,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3461</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -23791,7 +23791,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -23854,7 +23854,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3498</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -23869,7 +23869,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -23889,7 +23889,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4580</t>
+          <t>4405</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -23904,7 +23904,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>54,92%</t>
         </is>
       </c>
     </row>
@@ -23962,7 +23962,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -23997,12 +23997,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>2622</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7269</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -24012,12 +24012,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -24080,7 +24080,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -24095,7 +24095,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -24115,7 +24115,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -24130,7 +24130,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>33,12%</t>
         </is>
       </c>
     </row>
@@ -24684,7 +24684,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2677</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -24699,7 +24699,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>64,74%</t>
         </is>
       </c>
     </row>
@@ -24792,7 +24792,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>1100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -24807,7 +24807,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -24910,7 +24910,7 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2279</t>
+          <t>2067</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -24925,7 +24925,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>53,81%</t>
         </is>
       </c>
     </row>
@@ -26886,7 +26886,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>2531</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -26901,7 +26901,7 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -26956,7 +26956,7 @@
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -26971,7 +26971,7 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>51,19%</t>
         </is>
       </c>
     </row>
@@ -27069,7 +27069,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -27084,7 +27084,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>62,38%</t>
         </is>
       </c>
     </row>
@@ -27107,7 +27107,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>996</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -27122,7 +27122,7 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -27177,12 +27177,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4606</t>
+          <t>4516</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -27192,12 +27192,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>78,09%</t>
         </is>
       </c>
     </row>
@@ -27295,7 +27295,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -27310,7 +27310,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>65,82%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -27716,7 +27716,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -27731,7 +27731,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -27766,7 +27766,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -27794,7 +27794,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>51,09%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -27829,7 +27829,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>4525</t>
+          <t>4367</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -27844,7 +27844,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -27859,12 +27859,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>437</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -27874,12 +27874,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>54,14%</t>
         </is>
       </c>
     </row>
@@ -27902,12 +27902,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>609</t>
+          <t>648</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>3618</t>
+          <t>3613</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -27917,12 +27917,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -27957,7 +27957,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -27972,12 +27972,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1473</t>
+          <t>1639</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -27987,12 +27987,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -28020,7 +28020,7 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -28035,7 +28035,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -28050,12 +28050,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>797</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5335</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -28065,12 +28065,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -28085,12 +28085,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>1691</t>
+          <t>1604</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>7268</t>
+          <t>6791</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -28100,12 +28100,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -29266,12 +29266,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>690</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -29306,7 +29306,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3159</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -29321,7 +29321,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -29336,12 +29336,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>1039</t>
+          <t>938</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>6749</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -29351,12 +29351,12 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>16,39%</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29384,7 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>4143</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -29399,7 +29399,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -29414,12 +29414,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>8449</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -29429,12 +29429,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -29449,12 +29449,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>2502</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -29464,12 +29464,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>26,51%</t>
         </is>
       </c>
     </row>
@@ -29492,12 +29492,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>7170</t>
+          <t>7622</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>14049</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -29507,12 +29507,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -29527,12 +29527,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>8024</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>16847</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -29542,12 +29542,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -29562,12 +29562,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>17729</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>28988</t>
+          <t>28738</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -29577,12 +29577,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,78%</t>
         </is>
       </c>
     </row>
@@ -29605,12 +29605,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>744</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>5360</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -29620,12 +29620,12 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -29640,12 +29640,12 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11070</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
@@ -29655,12 +29655,12 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -29675,12 +29675,12 @@
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5215</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>14127</t>
+          <t>14011</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
@@ -29690,12 +29690,12 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,02%</t>
         </is>
       </c>
     </row>
